--- a/api/templates/device_activity/uk.xlsx
+++ b/api/templates/device_activity/uk.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\device_activity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B413E39-07C2-4847-8249-1164A43DC242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F39DCE-8DB8-4374-8EE5-E346B7708C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Підсумки діяльності" sheetId="1" r:id="rId1"/>
     <sheet name="Деталізація по пробам" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Оновлення останнього результату</t>
+  </si>
+  <si>
+    <t>аналіз</t>
   </si>
 </sst>
 </file>
@@ -554,78 +560,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.796875" customWidth="1"/>
     <col min="2" max="2" width="26.296875" customWidth="1"/>
-    <col min="3" max="3" width="21.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.19921875" customWidth="1"/>
     <col min="4" max="4" width="23.796875" customWidth="1"/>
     <col min="5" max="5" width="21.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
       <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>5</v>
       </c>
     </row>

--- a/api/templates/device_activity/uk.xlsx
+++ b/api/templates/device_activity/uk.xlsx
@@ -1,39 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\device_activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F39DCE-8DB8-4374-8EE5-E346B7708C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Підсумки діяльності" sheetId="1" r:id="rId1"/>
-    <sheet name="Деталізація по пробам" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Підсумки діяльності" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Деталізація по пробам" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+  <si>
+    <t>Активність пристрою</t>
+  </si>
+  <si>
+    <t>Дати: &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Області: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>Райони: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Сайти: &lt;Sites&gt;</t>
+  </si>
   <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Пристрій</t>
+  </si>
+  <si>
+    <t>Сайт</t>
+  </si>
+  <si>
+    <t>аналіз</t>
+  </si>
+  <si>
+    <t>Серіал</t>
+  </si>
+  <si>
+    <t>Оновлення останнього результату</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Статус технічного
+обслуговування</t>
+  </si>
+  <si>
+    <t>Статус</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;assayName&gt;</t>
+  </si>
+  <si>
     <t>&lt;serial&gt;</t>
   </si>
   <si>
@@ -46,84 +78,54 @@
     <t>&lt;deviceApprovalStatus&gt;</t>
   </si>
   <si>
-    <t>&lt;assayName&gt;</t>
-  </si>
-  <si>
-    <t>Дати: &lt;Dates&gt;</t>
-  </si>
-  <si>
-    <t>Райони: &lt;Lgas&gt;</t>
-  </si>
-  <si>
-    <t>Сайти: &lt;Sites&gt;</t>
-  </si>
-  <si>
-    <t>Активність пристрою</t>
-  </si>
-  <si>
-    <t>Пристрій</t>
-  </si>
-  <si>
-    <t>Серіал</t>
+    <t>Активність пристрою за аналізами</t>
+  </si>
+  <si>
+    <t>Аналіз</t>
   </si>
   <si>
     <t>Останнє завантаження</t>
   </si>
   <si>
     <t>Статус технічного обслуговування</t>
-  </si>
-  <si>
-    <t>Статус</t>
-  </si>
-  <si>
-    <t>Статус технічного
-обслуговування</t>
-  </si>
-  <si>
-    <t>Активність пристрою за аналізами</t>
-  </si>
-  <si>
-    <t>Аналіз</t>
-  </si>
-  <si>
-    <t>Області: &lt;States&gt;</t>
-  </si>
-  <si>
-    <t>Оновлення останнього результату</t>
-  </si>
-  <si>
-    <t>аналіз</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -149,18 +151,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -170,88 +164,20 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -559,176 +485,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.796875" customWidth="1"/>
-    <col min="2" max="2" width="26.296875" customWidth="1"/>
-    <col min="3" max="3" width="32.19921875" customWidth="1"/>
-    <col min="4" max="4" width="23.796875" customWidth="1"/>
-    <col min="5" max="5" width="21.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26.296875" customWidth="1"/>
+    <col min="4" max="4" width="32.19921875" customWidth="1"/>
+    <col min="5" max="5" width="23.796875" customWidth="1"/>
+    <col min="6" max="6" width="21.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="8.59765625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.19921875" customWidth="1"/>
-    <col min="2" max="2" width="12.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.8984375" customWidth="1"/>
-    <col min="4" max="4" width="26.8984375" customWidth="1"/>
-    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12.296875" customWidth="1"/>
+    <col min="4" max="4" width="13.8984375" customWidth="1"/>
+    <col min="5" max="5" width="26.8984375" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="7" width="21.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/uk.xlsx
+++ b/api/templates/device_activity/uk.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579484CA-675A-5143-90D2-92ECE91D8233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Підсумки діяльності" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Деталізація по пробам" state="visible" r:id="rId5"/>
+    <sheet name="Підсумки діяльності" sheetId="1" r:id="rId1"/>
+    <sheet name="Деталізація по пробам" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -50,7 +51,7 @@
     <t>Оновлення останнього результату</t>
   </si>
   <si>
-    <t xml:space="preserve">Статус технічного
+    <t>Статус технічного
 обслуговування</t>
   </si>
   <si>
@@ -93,39 +94,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -142,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -151,27 +153,65 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="slantDashDot">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,150 +525,150 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="11" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.796875" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="26.296875" customWidth="1"/>
-    <col min="4" max="4" width="32.19921875" customWidth="1"/>
-    <col min="5" max="5" width="23.796875" customWidth="1"/>
-    <col min="6" max="6" width="21.296875" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="4" width="26.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" defaultColWidth="8.59765625" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G113"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.19921875" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="12.296875" customWidth="1"/>
-    <col min="4" max="4" width="13.8984375" customWidth="1"/>
-    <col min="5" max="5" width="26.8984375" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="21.296875" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" customWidth="1"/>
+    <col min="4" max="4" width="37.1640625" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>21</v>
@@ -646,33 +686,346 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E42" s="9"/>
+    </row>
+    <row r="43" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E43" s="9"/>
+    </row>
+    <row r="44" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E45" s="9"/>
+    </row>
+    <row r="46" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E46" s="9"/>
+    </row>
+    <row r="47" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E47" s="9"/>
+    </row>
+    <row r="48" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E48" s="9"/>
+    </row>
+    <row r="49" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E49" s="9"/>
+    </row>
+    <row r="50" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E50" s="9"/>
+    </row>
+    <row r="51" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E51" s="9"/>
+    </row>
+    <row r="52" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E52" s="9"/>
+    </row>
+    <row r="53" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E53" s="9"/>
+    </row>
+    <row r="54" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E54" s="9"/>
+    </row>
+    <row r="55" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E55" s="9"/>
+    </row>
+    <row r="56" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E56" s="9"/>
+    </row>
+    <row r="57" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E58" s="9"/>
+    </row>
+    <row r="59" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E59" s="9"/>
+    </row>
+    <row r="60" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E60" s="9"/>
+    </row>
+    <row r="61" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E61" s="9"/>
+    </row>
+    <row r="62" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E62" s="9"/>
+    </row>
+    <row r="63" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E63" s="9"/>
+    </row>
+    <row r="64" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E64" s="9"/>
+    </row>
+    <row r="65" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E65" s="9"/>
+    </row>
+    <row r="66" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E66" s="9"/>
+    </row>
+    <row r="67" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E67" s="9"/>
+    </row>
+    <row r="68" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E68" s="9"/>
+    </row>
+    <row r="69" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E69" s="9"/>
+    </row>
+    <row r="70" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E70" s="9"/>
+    </row>
+    <row r="71" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E71" s="9"/>
+    </row>
+    <row r="72" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E72" s="9"/>
+    </row>
+    <row r="73" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E73" s="9"/>
+    </row>
+    <row r="74" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E74" s="9"/>
+    </row>
+    <row r="75" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E75" s="9"/>
+    </row>
+    <row r="76" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E76" s="9"/>
+    </row>
+    <row r="77" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E77" s="9"/>
+    </row>
+    <row r="78" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E78" s="9"/>
+    </row>
+    <row r="79" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E79" s="9"/>
+    </row>
+    <row r="80" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E80" s="9"/>
+    </row>
+    <row r="81" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E81" s="9"/>
+    </row>
+    <row r="82" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E82" s="9"/>
+    </row>
+    <row r="83" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E83" s="9"/>
+    </row>
+    <row r="84" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E84" s="9"/>
+    </row>
+    <row r="85" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E85" s="9"/>
+    </row>
+    <row r="86" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E86" s="9"/>
+    </row>
+    <row r="87" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E87" s="9"/>
+    </row>
+    <row r="88" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E88" s="9"/>
+    </row>
+    <row r="89" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E89" s="9"/>
+    </row>
+    <row r="90" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E90" s="9"/>
+    </row>
+    <row r="91" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E91" s="9"/>
+    </row>
+    <row r="92" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E92" s="9"/>
+    </row>
+    <row r="93" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E93" s="9"/>
+    </row>
+    <row r="94" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E94" s="9"/>
+    </row>
+    <row r="95" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E95" s="9"/>
+    </row>
+    <row r="96" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E96" s="9"/>
+    </row>
+    <row r="97" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E97" s="9"/>
+    </row>
+    <row r="98" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E98" s="9"/>
+    </row>
+    <row r="99" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E99" s="9"/>
+    </row>
+    <row r="100" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E100" s="9"/>
+    </row>
+    <row r="101" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E101" s="9"/>
+    </row>
+    <row r="102" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E102" s="9"/>
+    </row>
+    <row r="103" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E103" s="9"/>
+    </row>
+    <row r="104" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E104" s="9"/>
+    </row>
+    <row r="105" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E105" s="9"/>
+    </row>
+    <row r="106" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E106" s="9"/>
+    </row>
+    <row r="107" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E107" s="9"/>
+    </row>
+    <row r="108" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E108" s="9"/>
+    </row>
+    <row r="109" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E109" s="9"/>
+    </row>
+    <row r="110" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E110" s="9"/>
+    </row>
+    <row r="111" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E111" s="9"/>
+    </row>
+    <row r="112" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E112" s="9"/>
+    </row>
+    <row r="113" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E113" s="9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/uk.xlsx
+++ b/api/templates/device_activity/uk.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579484CA-675A-5143-90D2-92ECE91D8233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="Підсумки діяльності" sheetId="1" r:id="rId1"/>
-    <sheet name="Деталізація по пробам" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Підсумки діяльності" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Деталізація по пробам" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>Активність пристрою</t>
   </si>
@@ -33,15 +32,18 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Сайт</t>
+  </si>
+  <si>
     <t>Пристрій</t>
   </si>
   <si>
-    <t>Сайт</t>
-  </si>
-  <si>
     <t>аналіз</t>
   </si>
   <si>
@@ -51,17 +53,17 @@
     <t>Оновлення останнього результату</t>
   </si>
   <si>
-    <t>Статус технічного
+    <t xml:space="preserve">Статус технічного
 обслуговування</t>
   </si>
   <si>
     <t>Статус</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;assayName&gt;</t>
@@ -94,40 +96,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -153,33 +155,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="slantDashDot">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="slantDashDot"/>
       <diagonal/>
     </border>
     <border>
@@ -195,6 +174,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -206,11 +192,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -525,107 +511,112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="4" width="26.1640625" customWidth="1"/>
     <col min="5" max="5" width="18.1640625" customWidth="1"/>
-    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="16.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+      <c r="G9" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.6640625" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -636,396 +627,401 @@
     <col min="7" max="7" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="B7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="F7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="E8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G8" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E10" s="9"/>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E11" s="9"/>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E14" s="9"/>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E16" s="9"/>
     </row>
-    <row r="17" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E17" s="9"/>
     </row>
-    <row r="18" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E18" s="9"/>
     </row>
-    <row r="19" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E19" s="9"/>
     </row>
-    <row r="20" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" s="9"/>
     </row>
-    <row r="21" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E22" s="9"/>
     </row>
-    <row r="23" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E23" s="9"/>
     </row>
-    <row r="24" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E24" s="9"/>
     </row>
-    <row r="25" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E26" s="9"/>
     </row>
-    <row r="27" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E27" s="9"/>
     </row>
-    <row r="28" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E28" s="9"/>
     </row>
-    <row r="29" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E29" s="9"/>
     </row>
-    <row r="30" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E30" s="9"/>
     </row>
-    <row r="31" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E32" s="9"/>
     </row>
-    <row r="33" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E41" s="9"/>
     </row>
-    <row r="42" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E42" s="9"/>
     </row>
-    <row r="43" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E43" s="9"/>
     </row>
-    <row r="44" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E44" s="9"/>
     </row>
-    <row r="45" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E45" s="9"/>
     </row>
-    <row r="46" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E46" s="9"/>
     </row>
-    <row r="47" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E47" s="9"/>
     </row>
-    <row r="48" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E48" s="9"/>
     </row>
-    <row r="49" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E49" s="9"/>
     </row>
-    <row r="50" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E50" s="9"/>
     </row>
-    <row r="51" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E51" s="9"/>
     </row>
-    <row r="52" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E52" s="9"/>
     </row>
-    <row r="53" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E53" s="9"/>
     </row>
-    <row r="54" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E54" s="9"/>
     </row>
-    <row r="55" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E55" s="9"/>
     </row>
-    <row r="56" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E56" s="9"/>
     </row>
-    <row r="57" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E57" s="9"/>
     </row>
-    <row r="58" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E58" s="9"/>
     </row>
-    <row r="59" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E59" s="9"/>
     </row>
-    <row r="60" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E60" s="9"/>
     </row>
-    <row r="61" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E61" s="9"/>
     </row>
-    <row r="62" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E62" s="9"/>
     </row>
-    <row r="63" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E63" s="9"/>
     </row>
-    <row r="64" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E64" s="9"/>
     </row>
-    <row r="65" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E65" s="9"/>
     </row>
-    <row r="66" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E66" s="9"/>
     </row>
-    <row r="67" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E67" s="9"/>
     </row>
-    <row r="68" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E68" s="9"/>
     </row>
-    <row r="69" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E69" s="9"/>
     </row>
-    <row r="70" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E70" s="9"/>
     </row>
-    <row r="71" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E71" s="9"/>
     </row>
-    <row r="72" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E72" s="9"/>
     </row>
-    <row r="73" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E73" s="9"/>
     </row>
-    <row r="74" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E74" s="9"/>
     </row>
-    <row r="75" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E75" s="9"/>
     </row>
-    <row r="76" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E76" s="9"/>
     </row>
-    <row r="77" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E77" s="9"/>
     </row>
-    <row r="78" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E78" s="9"/>
     </row>
-    <row r="79" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E79" s="9"/>
     </row>
-    <row r="80" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E80" s="9"/>
     </row>
-    <row r="81" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E81" s="9"/>
     </row>
-    <row r="82" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E82" s="9"/>
     </row>
-    <row r="83" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E83" s="9"/>
     </row>
-    <row r="84" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E84" s="9"/>
     </row>
-    <row r="85" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E85" s="9"/>
     </row>
-    <row r="86" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E86" s="9"/>
     </row>
-    <row r="87" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E87" s="9"/>
     </row>
-    <row r="88" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E88" s="9"/>
     </row>
-    <row r="89" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E89" s="9"/>
     </row>
-    <row r="90" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E90" s="9"/>
     </row>
-    <row r="91" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E91" s="9"/>
     </row>
-    <row r="92" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E92" s="9"/>
     </row>
-    <row r="93" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E93" s="9"/>
     </row>
-    <row r="94" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E94" s="9"/>
     </row>
-    <row r="95" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E95" s="9"/>
     </row>
-    <row r="96" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E96" s="9"/>
     </row>
-    <row r="97" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E97" s="9"/>
     </row>
-    <row r="98" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E98" s="9"/>
     </row>
-    <row r="99" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E99" s="9"/>
     </row>
-    <row r="100" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E100" s="9"/>
     </row>
-    <row r="101" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E101" s="9"/>
     </row>
-    <row r="102" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E102" s="9"/>
     </row>
-    <row r="103" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E103" s="9"/>
     </row>
-    <row r="104" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E104" s="9"/>
     </row>
-    <row r="105" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E105" s="9"/>
     </row>
-    <row r="106" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E106" s="9"/>
     </row>
-    <row r="107" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E107" s="9"/>
     </row>
-    <row r="108" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E108" s="9"/>
     </row>
-    <row r="109" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E109" s="9"/>
     </row>
-    <row r="110" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E110" s="9"/>
     </row>
-    <row r="111" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E111" s="9"/>
     </row>
-    <row r="112" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E112" s="9"/>
     </row>
-    <row r="113" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E113" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/uk.xlsx
+++ b/api/templates/device_activity/uk.xlsx
@@ -185,16 +185,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -650,7 +649,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -660,25 +659,25 @@
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -695,7 +694,7 @@
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -706,319 +705,319 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E9" s="9"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="9"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="9"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="9"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="9"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E14" s="9"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E15" s="9"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="9"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="9"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="9"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="9"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="9"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="9"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="9"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="9"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="9"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="9"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="9"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="9"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="9"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="9"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="9"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="9"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="9"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="9"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="9"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="9"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="9"/>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="9"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="9"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="9"/>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="9"/>
+      <c r="E40" s="10"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="9"/>
+      <c r="E41" s="10"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="9"/>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="9"/>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="9"/>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="9"/>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="9"/>
+      <c r="E46" s="10"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="9"/>
+      <c r="E47" s="10"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="9"/>
+      <c r="E48" s="10"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="9"/>
+      <c r="E49" s="10"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="9"/>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="9"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="9"/>
+      <c r="E52" s="10"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="9"/>
+      <c r="E53" s="10"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="9"/>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="9"/>
+      <c r="E55" s="10"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="9"/>
+      <c r="E56" s="10"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="9"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="9"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="9"/>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="9"/>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="9"/>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="9"/>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="9"/>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="9"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="9"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="9"/>
+      <c r="E66" s="10"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="9"/>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="9"/>
+      <c r="E68" s="10"/>
     </row>
     <row r="69" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="9"/>
+      <c r="E69" s="10"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="9"/>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="9"/>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="9"/>
+      <c r="E72" s="10"/>
     </row>
     <row r="73" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="9"/>
+      <c r="E73" s="10"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="9"/>
+      <c r="E74" s="10"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="9"/>
+      <c r="E75" s="10"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="9"/>
+      <c r="E76" s="10"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="9"/>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="9"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="9"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="9"/>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="9"/>
+      <c r="E81" s="10"/>
     </row>
     <row r="82" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="9"/>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="9"/>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="9"/>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="9"/>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="9"/>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="9"/>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="9"/>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="9"/>
+      <c r="E89" s="10"/>
     </row>
     <row r="90" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="9"/>
+      <c r="E90" s="10"/>
     </row>
     <row r="91" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="9"/>
+      <c r="E91" s="10"/>
     </row>
     <row r="92" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="9"/>
+      <c r="E92" s="10"/>
     </row>
     <row r="93" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="9"/>
+      <c r="E93" s="10"/>
     </row>
     <row r="94" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="9"/>
+      <c r="E94" s="10"/>
     </row>
     <row r="95" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="9"/>
+      <c r="E95" s="10"/>
     </row>
     <row r="96" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="9"/>
+      <c r="E96" s="10"/>
     </row>
     <row r="97" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="9"/>
+      <c r="E97" s="10"/>
     </row>
     <row r="98" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="9"/>
+      <c r="E98" s="10"/>
     </row>
     <row r="99" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="9"/>
+      <c r="E99" s="10"/>
     </row>
     <row r="100" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="9"/>
+      <c r="E100" s="10"/>
     </row>
     <row r="101" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="9"/>
+      <c r="E101" s="10"/>
     </row>
     <row r="102" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="9"/>
+      <c r="E102" s="10"/>
     </row>
     <row r="103" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="9"/>
+      <c r="E103" s="10"/>
     </row>
     <row r="104" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="9"/>
+      <c r="E104" s="10"/>
     </row>
     <row r="105" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="9"/>
+      <c r="E105" s="10"/>
     </row>
     <row r="106" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="9"/>
+      <c r="E106" s="10"/>
     </row>
     <row r="107" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E107" s="9"/>
+      <c r="E107" s="10"/>
     </row>
     <row r="108" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E108" s="9"/>
+      <c r="E108" s="10"/>
     </row>
     <row r="109" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E109" s="9"/>
+      <c r="E109" s="10"/>
     </row>
     <row r="110" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E110" s="9"/>
+      <c r="E110" s="10"/>
     </row>
     <row r="111" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E111" s="9"/>
+      <c r="E111" s="10"/>
     </row>
     <row r="112" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="9"/>
+      <c r="E112" s="10"/>
     </row>
     <row r="113" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="9"/>
+      <c r="E113" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/api/templates/device_activity/uk.xlsx
+++ b/api/templates/device_activity/uk.xlsx
@@ -32,7 +32,7 @@
     <t>Сайти: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Виведені з експлуатації пристрої: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -185,15 +185,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -649,7 +648,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -659,25 +658,25 @@
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -694,7 +693,7 @@
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -705,319 +704,319 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E9" s="10"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="10"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="10"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="10"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="10"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E15" s="10"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="10"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="10"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="10"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="10"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="10"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="10"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="10"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="10"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="10"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="10"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="10"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="10"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="10"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="10"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="10"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="10"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="10"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="10"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="10"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="10"/>
+      <c r="E35" s="9"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="10"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="10"/>
+      <c r="E37" s="9"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="10"/>
+      <c r="E38" s="9"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="10"/>
+      <c r="E39" s="9"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="10"/>
+      <c r="E40" s="9"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="10"/>
+      <c r="E41" s="9"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="10"/>
+      <c r="E42" s="9"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="10"/>
+      <c r="E43" s="9"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="10"/>
+      <c r="E44" s="9"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="10"/>
+      <c r="E45" s="9"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="10"/>
+      <c r="E46" s="9"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="10"/>
+      <c r="E47" s="9"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="10"/>
+      <c r="E48" s="9"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="10"/>
+      <c r="E49" s="9"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="10"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="10"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="10"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="10"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="10"/>
+      <c r="E54" s="9"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="10"/>
+      <c r="E55" s="9"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="10"/>
+      <c r="E56" s="9"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="10"/>
+      <c r="E57" s="9"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="10"/>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="10"/>
+      <c r="E59" s="9"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="10"/>
+      <c r="E60" s="9"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="10"/>
+      <c r="E61" s="9"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="10"/>
+      <c r="E62" s="9"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="10"/>
+      <c r="E63" s="9"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="10"/>
+      <c r="E64" s="9"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="10"/>
+      <c r="E65" s="9"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="10"/>
+      <c r="E66" s="9"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="10"/>
+      <c r="E67" s="9"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="10"/>
+      <c r="E68" s="9"/>
     </row>
     <row r="69" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="10"/>
+      <c r="E69" s="9"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="10"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="10"/>
+      <c r="E71" s="9"/>
     </row>
     <row r="72" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="10"/>
+      <c r="E72" s="9"/>
     </row>
     <row r="73" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="10"/>
+      <c r="E73" s="9"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="10"/>
+      <c r="E74" s="9"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="10"/>
+      <c r="E75" s="9"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="10"/>
+      <c r="E76" s="9"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="10"/>
+      <c r="E77" s="9"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="10"/>
+      <c r="E78" s="9"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="10"/>
+      <c r="E79" s="9"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="10"/>
+      <c r="E80" s="9"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="10"/>
+      <c r="E81" s="9"/>
     </row>
     <row r="82" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="10"/>
+      <c r="E82" s="9"/>
     </row>
     <row r="83" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="10"/>
+      <c r="E83" s="9"/>
     </row>
     <row r="84" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="10"/>
+      <c r="E84" s="9"/>
     </row>
     <row r="85" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="10"/>
+      <c r="E85" s="9"/>
     </row>
     <row r="86" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="10"/>
+      <c r="E86" s="9"/>
     </row>
     <row r="87" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="10"/>
+      <c r="E87" s="9"/>
     </row>
     <row r="88" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="10"/>
+      <c r="E88" s="9"/>
     </row>
     <row r="89" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="10"/>
+      <c r="E89" s="9"/>
     </row>
     <row r="90" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="10"/>
+      <c r="E90" s="9"/>
     </row>
     <row r="91" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="10"/>
+      <c r="E91" s="9"/>
     </row>
     <row r="92" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="10"/>
+      <c r="E92" s="9"/>
     </row>
     <row r="93" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="10"/>
+      <c r="E93" s="9"/>
     </row>
     <row r="94" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="10"/>
+      <c r="E94" s="9"/>
     </row>
     <row r="95" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="10"/>
+      <c r="E95" s="9"/>
     </row>
     <row r="96" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="10"/>
+      <c r="E96" s="9"/>
     </row>
     <row r="97" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="10"/>
+      <c r="E97" s="9"/>
     </row>
     <row r="98" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="10"/>
+      <c r="E98" s="9"/>
     </row>
     <row r="99" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="10"/>
+      <c r="E99" s="9"/>
     </row>
     <row r="100" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="10"/>
+      <c r="E100" s="9"/>
     </row>
     <row r="101" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="10"/>
+      <c r="E101" s="9"/>
     </row>
     <row r="102" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="10"/>
+      <c r="E102" s="9"/>
     </row>
     <row r="103" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="10"/>
+      <c r="E103" s="9"/>
     </row>
     <row r="104" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="10"/>
+      <c r="E104" s="9"/>
     </row>
     <row r="105" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="10"/>
+      <c r="E105" s="9"/>
     </row>
     <row r="106" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="10"/>
+      <c r="E106" s="9"/>
     </row>
     <row r="107" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E107" s="10"/>
+      <c r="E107" s="9"/>
     </row>
     <row r="108" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E108" s="10"/>
+      <c r="E108" s="9"/>
     </row>
     <row r="109" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E109" s="10"/>
+      <c r="E109" s="9"/>
     </row>
     <row r="110" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E110" s="10"/>
+      <c r="E110" s="9"/>
     </row>
     <row r="111" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E111" s="10"/>
+      <c r="E111" s="9"/>
     </row>
     <row r="112" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="10"/>
+      <c r="E112" s="9"/>
     </row>
     <row r="113" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="10"/>
+      <c r="E113" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
